--- a/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 거의 매일 정말 지친다고 느껴서 왔어요. 밤에 푹 자고 나도, 아침에 일어나면 몸이랑 머리가 여전히 무겁게 처지는 느낌이 들고, 그런 상태로 계산원 근무를 하러 나가야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 평소보다 에너지가 떨어졌다고 느끼시거나, 쉬어도 피로감을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 거의 그런 것 같아요. 밤새 자도 대부분 날 지친 느낌이에요. 계산원 근무 때문에 일어나면, 몸이랑 머리가 여전히 처지는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 예전보다 즐거움을 덜 느끼거나 평소 즐기던 활동에 흥미가 줄었다고 느끼신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 그런 큰 변화는 딱히 못 느꼈어요. 평소 하던 걸 여전히 다 하고 있어요, 그냥 하면서 좀 피곤한 것뿐일 수도 있고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 범불안장애 (D011); 지속성 우울장애 (D014) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 하루 중 대부분의 시간을, 대부분의 날에 기분이 가라앉거나 우울하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그렇진 않은 것 같아요. 그러니까, 지치고 좀 처지는 느낌은 있는데, 하루 대부분을 우울하다고까지는 못 하겠어요. 적어도 제가 딱히 느낀 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 잠들기 어렵거나, 잠을 유지하기 어렵거나, 아니면 여전히 피곤한데도 평소보다 훨씬 더 많이 주무시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 그래요. 대부분의 밤에 침대에 누울 때는 피곤한데, 그러다 머릿속이 청구서, 근무 일정, 집에 있는 사람들이 다 괜찮은지 같은 생각들로 흘러가기 시작해요. 결국엔 잠들긴 하는데, 여전히 제대로 가라앉지 못한 느낌으로 일어나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 예전에 즐기던 활동들을 포함해서 대부분의 활동에 흥미나 즐거움이 줄었다고 느끼신 적이 있으신가요, 그리고 그게 얼마나 오래됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그런 게 일어나고 있다고는 잘 모르겠어요. 대부분의 것에 흥미를 잃었다거나 더 이상 즐기지 못한다는 걸 딱히 못 느꼈어요. 오히려 그냥 가끔 피곤한 것뿐이지, 여전히 평소 하던 걸 하고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 집중력이나 주의력에 변화가 있으신가요, 예를 들어 할 일에 집중을 유지하거나 결정을 내리는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네, 가끔요. 직장에서 계산대에 서서 화면을 똑바로 보고 있는데도, 머릿속은 집안일이나 청구서 생각에 가 있어서 놓쳐버려요. 그러면 서랍을 다시 세거나 제가 한 작은 실수를 알아차리게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 밤에 충분히 잤다고 생각되는데도 낮 동안 지나치게 졸린다고 느끼신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 낮에 많이 지친다고 느껴요. 밤에 충분히 잤다고 생각해도, 일어나면 몸이랑 머리가 여전히 처지는 느낌이에요, 특히 계산원 근무를 준비할 때요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 식욕에 변화가 있으셨나요, 예를 들어 평소보다 덜 먹거나 의도치 않게 체중이 줄거나 하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 그런 것 같지 않아요. 식욕은 거의 평소랑 비슷하고, 의도치 않게 살이 빠진 것도 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 밤에 자주 깨시거나 잠을 유지하기 어려우신가요, 아니면 딱히 많이 깨지는 않는데도 수면이 개운하지 않은 느낌이신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 대부분의 밤에 피곤한 채로 침대에 눕는데, 제대로 가라앉지가 않아요. 청구서, 근무 일정, 집이 다 괜찮은지 같은 생각을 하면서 누워 있어요. 잠은 들긴 하는데 개운하지 않은 느낌이에요, 마치 제대로 쉬지 못한 채로 일어나는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 잠드는 데 어려움을 겪거나 수면이 개운하지 않다고 느끼는 게 얼마나 자주 있으신가요—일주일에 적어도 세 번 정도인가요, 그리고 이게 한 달 넘게 지속되고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 솔직히 거의 매일 밤이에요. 피곤한 채로 침대에 눕는데, 그러다 청구서, 근무 일정, 집에 있는 사람들이 다 괜찮은지 생각하면서 누워 있어요. 잠이 들어도 제대로 가라앉지 못한 느낌으로 일어나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 밤중에 많이 깨지 않더라도, 잠자리에 들 때만큼 여전히 피곤한 느낌으로 일어나는, 그런 회복되지 않는 수면이라고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 거의 그래요. 많이 깼던 기억이 없어도, 일어나면 제대로 가라앉지 못한 느낌이에요. 피곤한 채로 잠자리에 들지만, 머릿속에서는 계속 청구서랑 일, 집안일 생각을 하게 돼서 잠이 그다지 도움이 안 되는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 충분히 쉬었다고 느껴질 때조차 그 피로감이 하루를 보내는 데 어떤 영향을 주는지 설명해주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 거의 매일 지친다고 느껴요. 충분히 잤다고 생각해도, 일어나면 몸이랑 머리가 여전히 처져 있어요. 계산원 근무를 준비할 때쯤이면 이미 새롭게 하루를 시작하는 게 아니라 억지로 하루를 밀어붙이고 있는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 몸이나 정신적으로 특별히 힘든 일을 하지 않았을 때도, 에너지 부족이나 피로감이 대부분의 날에 나타난다고 하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 대부분의 날에요. 딱히 많은 걸 하지 않았을 때도 여전히 지친 느낌이에요. 밤에 푹 자고도, 일어나면 몸이랑 머리가 처져 있어요, 마치 계산원 근무를 시작하기도 전에 이미 지쳐 있는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 머릿속이 피곤하거나 압도된 느낌 때문에 간단한 일조차 명료하게 생각하거나 집중하기 어려우신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네, 그래요. 계산대에서 간단한 일을 할 때도, 화면을 똑바로 보고 있는데 청구서나 집안일 생각을 하다가 놓쳐버려요. 그러면 서랍을 다시 세거나 작은 실수를 알아채게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 기분이 비교적 안정적이고 딱히 스트레스받거나 가라앉아 있지 않을 때도 피로감과 개운하지 않은 수면이 나타나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네, 딱히 속상하거나 그런 게 없을 때도 여전히 지친 느낌이에요. 밤새 푹 잔 것 같아도, 계산원 근무를 하러 일어나면 몸이랑 머리가 여전히 처져 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 지난 2주 동안, 딱히 피곤하지 않을 때도 며칠씩 기분이 가라앉거나 흥미를 잃은 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나처럼 안 좋은 날이 있긴 한데, 그렇게 며칠 연달아 가라앉거나 흥미를 잃은 건 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 지난 2주 동안, 딱히 피곤하지 않을 때도 활동에 대한 흥미를 잃거나 즐거움을 덜 느끼신 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 그런 것 같지 않아요, 딱히요. 그러니까, 뭔가를 안 한다면 보통 피곤하거나 산만해서 그런 건데, 더 이상 뭘 즐기지 못한다고는 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 딱히 가라앉거나 스트레스받고 있지 않을 때도, 일을 시작하기 힘들거나 모든 게 유난히 더 힘들게 느껴지는 걸 알아챈 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네, 가끔 그렇게 느껴요. 대부분은 그냥 거의 매일 지쳐 있는 느낌이에요. 밤에 푹 자고도, 계산원 근무를 하러 일어나면 몸이랑 머리가 여전히 처져 있어서, 뭔가를 시작하는 데 필요 이상으로 힘이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 범불안장애 (D011)
 인구통계: 성별 남성 / 나이 35 / 직업상태 cashier / 최종학력 고등학교 졸업
@@ -575,467 +978,36 @@
 증상 지속 기간: 1 year and 3 months
 추가 요건: 
 주호소 증상 코드: S029
-배경 서술: 그레고리와 그의 아내는 더 안정적인 보살핌이 필요한 손위 친척을 집으로 모셨고, 처음에 그는 이를 자신이 자라온 가족과 교회의 가치관이 자연스럽게 이어지는 것으로 받아들였다. 이후 1년 3개월에 걸쳐 그의 걱정은 새로운 돌봄 일과에서 시작해 점차 돈, 근무 일정, 가정의 화목, 교회 활동, 그리고 자신이 누군가를 실망시키고 있는 건 아닌지에 대한 문제로까지 번져갔고, 그 걱정을 제쳐두기가 점점 더 어려워졌다. 지속적인 걱정은 수면의 질과 낮 동안의 에너지, 계산대에서의 집중력에 영향을 미치기 시작해 사소한 현금 계산 실수와 푸드뱅크 봉사 시간 감소로 이어졌지만, 그는 애를 써가며 계속 일상을 유지해나갔다. 그는 정기 1차 진료 방문에서 피로감과 수면 장애를 언급했고, 지속적이고 통제되지 않는 걱정이라는 전반적인 병력이 정신과 의뢰로 이어졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 거의 매일 정말 지친다고 느껴서 왔어요. 밤에 푹 자고 나도, 아침에 일어나면 몸이랑 머리가 여전히 무겁게 처지는 느낌이 들고, 그런 상태로 계산원 근무를 하러 나가야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 평소보다 에너지가 떨어졌다고 느끼시거나, 쉬어도 피로감을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 거의 그런 것 같아요. 밤새 자도 대부분 날 지친 느낌이에요. 계산원 근무 때문에 일어나면, 몸이랑 머리가 여전히 처지는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 예전보다 즐거움을 덜 느끼거나 평소 즐기던 활동에 흥미가 줄었다고 느끼신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 그런 큰 변화는 딱히 못 느꼈어요. 평소 하던 걸 여전히 다 하고 있어요, 그냥 하면서 좀 피곤한 것뿐일 수도 있고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 지속성 우울장애 (D014) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 하루 중 대부분의 시간을, 대부분의 날에 기분이 가라앉거나 우울하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그렇진 않은 것 같아요. 그러니까, 지치고 좀 처지는 느낌은 있는데, 하루 대부분을 우울하다고까지는 못 하겠어요. 적어도 제가 딱히 느낀 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 잠들기 어렵거나, 잠을 유지하기 어렵거나, 아니면 여전히 피곤한데도 평소보다 훨씬 더 많이 주무시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 그래요. 대부분의 밤에 침대에 누울 때는 피곤한데, 그러다 머릿속이 청구서, 근무 일정, 집에 있는 사람들이 다 괜찮은지 같은 생각들로 흘러가기 시작해요. 결국엔 잠들긴 하는데, 여전히 제대로 가라앉지 못한 느낌으로 일어나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 예전에 즐기던 활동들을 포함해서 대부분의 활동에 흥미나 즐거움이 줄었다고 느끼신 적이 있으신가요, 그리고 그게 얼마나 오래됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그런 게 일어나고 있다고는 잘 모르겠어요. 대부분의 것에 흥미를 잃었다거나 더 이상 즐기지 못한다는 걸 딱히 못 느꼈어요. 오히려 그냥 가끔 피곤한 것뿐이지, 여전히 평소 하던 걸 하고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 집중력이나 주의력에 변화가 있으신가요, 예를 들어 할 일에 집중을 유지하거나 결정을 내리는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네, 가끔요. 직장에서 계산대에 서서 화면을 똑바로 보고 있는데도, 머릿속은 집안일이나 청구서 생각에 가 있어서 놓쳐버려요. 그러면 서랍을 다시 세거나 제가 한 작은 실수를 알아차리게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 밤에 충분히 잤다고 생각되는데도 낮 동안 지나치게 졸린다고 느끼신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 낮에 많이 지친다고 느껴요. 밤에 충분히 잤다고 생각해도, 일어나면 몸이랑 머리가 여전히 처지는 느낌이에요, 특히 계산원 근무를 준비할 때요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 식욕에 변화가 있으셨나요, 예를 들어 평소보다 덜 먹거나 의도치 않게 체중이 줄거나 하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 그런 것 같지 않아요. 식욕은 거의 평소랑 비슷하고, 의도치 않게 살이 빠진 것도 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 밤에 자주 깨시거나 잠을 유지하기 어려우신가요, 아니면 딱히 많이 깨지는 않는데도 수면이 개운하지 않은 느낌이신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 대부분의 밤에 피곤한 채로 침대에 눕는데, 제대로 가라앉지가 않아요. 청구서, 근무 일정, 집이 다 괜찮은지 같은 생각을 하면서 누워 있어요. 잠은 들긴 하는데 개운하지 않은 느낌이에요, 마치 제대로 쉬지 못한 채로 일어나는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 잠드는 데 어려움을 겪거나 수면이 개운하지 않다고 느끼는 게 얼마나 자주 있으신가요—일주일에 적어도 세 번 정도인가요, 그리고 이게 한 달 넘게 지속되고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 솔직히 거의 매일 밤이에요. 피곤한 채로 침대에 눕는데, 그러다 청구서, 근무 일정, 집에 있는 사람들이 다 괜찮은지 생각하면서 누워 있어요. 잠이 들어도 제대로 가라앉지 못한 느낌으로 일어나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 밤중에 많이 깨지 않더라도, 잠자리에 들 때만큼 여전히 피곤한 느낌으로 일어나는, 그런 회복되지 않는 수면이라고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 거의 그래요. 많이 깼던 기억이 없어도, 일어나면 제대로 가라앉지 못한 느낌이에요. 피곤한 채로 잠자리에 들지만, 머릿속에서는 계속 청구서랑 일, 집안일 생각을 하게 돼서 잠이 그다지 도움이 안 되는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 충분히 쉬었다고 느껴질 때조차 그 피로감이 하루를 보내는 데 어떤 영향을 주는지 설명해주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 거의 매일 지친다고 느껴요. 충분히 잤다고 생각해도, 일어나면 몸이랑 머리가 여전히 처져 있어요. 계산원 근무를 준비할 때쯤이면 이미 새롭게 하루를 시작하는 게 아니라 억지로 하루를 밀어붙이고 있는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 몸이나 정신적으로 특별히 힘든 일을 하지 않았을 때도, 에너지 부족이나 피로감이 대부분의 날에 나타난다고 하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 대부분의 날에요. 딱히 많은 걸 하지 않았을 때도 여전히 지친 느낌이에요. 밤에 푹 자고도, 일어나면 몸이랑 머리가 처져 있어요, 마치 계산원 근무를 시작하기도 전에 이미 지쳐 있는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 머릿속이 피곤하거나 압도된 느낌 때문에 간단한 일조차 명료하게 생각하거나 집중하기 어려우신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네, 그래요. 계산대에서 간단한 일을 할 때도, 화면을 똑바로 보고 있는데 청구서나 집안일 생각을 하다가 놓쳐버려요. 그러면 서랍을 다시 세거나 작은 실수를 알아채게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 기분이 비교적 안정적이고 딱히 스트레스받거나 가라앉아 있지 않을 때도 피로감과 개운하지 않은 수면이 나타나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네, 딱히 속상하거나 그런 게 없을 때도 여전히 지친 느낌이에요. 밤새 푹 잔 것 같아도, 계산원 근무를 하러 일어나면 몸이랑 머리가 여전히 처져 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 지난 2주 동안, 딱히 피곤하지 않을 때도 며칠씩 기분이 가라앉거나 흥미를 잃은 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나처럼 안 좋은 날이 있긴 한데, 그렇게 며칠 연달아 가라앉거나 흥미를 잃은 건 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 지난 2주 동안, 딱히 피곤하지 않을 때도 활동에 대한 흥미를 잃거나 즐거움을 덜 느끼신 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 그런 것 같지 않아요, 딱히요. 그러니까, 뭔가를 안 한다면 보통 피곤하거나 산만해서 그런 건데, 더 이상 뭘 즐기지 못한다고는 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 딱히 가라앉거나 스트레스받고 있지 않을 때도, 일을 시작하기 힘들거나 모든 게 유난히 더 힘들게 느껴지는 걸 알아챈 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네, 가끔 그렇게 느껴요. 대부분은 그냥 거의 매일 지쳐 있는 느낌이에요. 밤에 푹 자고도, 계산원 근무를 하러 일어나면 몸이랑 머리가 여전히 처져 있어서, 뭔가를 시작하는 데 필요 이상으로 힘이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: 그레고리와 그의 아내는 더 안정적인 보살핌이 필요한 손위 친척을 집으로 모셨고, 처음에 그는 이를 자신이 자라온 가족과 교회의 가치관이 자연스럽게 이어지는 것으로 받아들였다. 이후 1년 3개월에 걸쳐 그의 걱정은 새로운 돌봄 일과에서 시작해 점차 돈, 근무 일정, 가정의 화목, 교회 활동, 그리고 자신이 누군가를 실망시키고 있는 건 아닌지에 대한 문제로까지 번져갔고, 그 걱정을 제쳐두기가 점점 더 어려워졌다. 지속적인 걱정은 수면의 질과 낮 동안의 에너지, 계산대에서의 집중력에 영향을 미치기 시작해 사소한 현금 계산 실수와 푸드뱅크 봉사 시간 감소로 이어졌지만, 그는 애를 써가며 계속 일상을 유지해나갔다. 그는 정기 1차 진료 방문에서 피로감과 수면 장애를 언급했고, 지속적이고 통제되지 않는 걱정이라는 전반적인 병력이 정신과 의뢰로 이어졌다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S056 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - S057 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - S059 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 범불안장애 (D011); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: G47.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.; 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.
-  누락: 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.; 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.; 과민성: 사소한 자극에도 민감하거나 날카롭게 반응하는 상태.; 근육 긴장: 근육이 지속적으로 긴장되고 뻣뻣하며 불편감을 동반하는 상태.</t>
+          <t>의사의 최종 진단: None (None, ICD: G47.0)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1003,11 +1008,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S004_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0426</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
